--- a/output/laminas_comunales/comunal_s_fonasa_a_2022_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2022_antofagasta.xlsx
@@ -375,31 +375,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Taltal</t>
         </is>
       </c>
       <c r="C2">
-        <v>284911</v>
+        <v>90.0359135019485</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Calama</t>
+          <t>San Pedro de Atacama</t>
         </is>
       </c>
       <c r="C3">
-        <v>131222</v>
+        <v>84.95003532855557</v>
       </c>
     </row>
     <row r="4">
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>22459</v>
+        <v>83.36983555440068</v>
       </c>
     </row>
     <row r="5">
@@ -429,67 +429,67 @@
         </is>
       </c>
       <c r="C5">
-        <v>12945</v>
+        <v>82.50478011472275</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Taltal</t>
+          <t>Ollagüe</t>
         </is>
       </c>
       <c r="C6">
-        <v>11783</v>
+        <v>79.71698113207547</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
+          <t>Sierra Gorda</t>
         </is>
       </c>
       <c r="C7">
-        <v>8416</v>
+        <v>79.6308954203691</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sierra Gorda</t>
+          <t>Calama</t>
         </is>
       </c>
       <c r="C8">
-        <v>1165</v>
+        <v>72.69957174277974</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ollagüe</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="C9">
-        <v>169</v>
+        <v>70.7563359119864</v>
       </c>
     </row>
   </sheetData>
@@ -545,7 +545,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_fonasa_a_2022_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2022_antofagasta.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C273"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -490,6 +490,3966 @@
       </c>
       <c r="C9">
         <v>70.7563359119864</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>45.93721610982134</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>45.42675937953695</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>44.60915412241155</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>43.42031998218197</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>42.99384825700615</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>42.49840662842575</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>41.50943396226415</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>40.00637348629701</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>39.94951557221871</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>39.01281921873423</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>38.20754716981132</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>38.14702574529499</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>37.24212434654117</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>36.63704716336295</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>34.55254599748475</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>33.51421156544522</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>31.25557680050988</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>31.21025537498738</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>30.21189336978811</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>29.01352487201039</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>26.98574507337991</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>26.597355405269</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>26.41509433962264</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>26.28159916849178</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>25.94339622641509</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>25.85842087679572</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>25.61359939403723</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>25.00955146328418</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>24.5092770597067</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>24.28023294798406</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>22.72832255100394</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>22.5685149776928</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>22.48156499481992</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>22.28298017771702</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>22.16981132075472</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>19.82627417498794</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>18.52219760067242</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>17.96709397395781</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>17.72484102149995</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>17.49063956598151</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>17.22488038277512</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>17.16971039963322</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>16.62274026504324</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>16.61567877629063</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>16.50943396226415</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>16.50943396226415</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>16.30975143403442</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>15.30231149692137</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>15.10516252390057</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>15.03759398496241</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>14.77071895135153</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>14.69583048530417</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>14.36358130614717</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>14.05270943329326</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>13.89164820050432</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>13.75436156606608</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>13.29070070654266</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>13.24845020230892</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>13.23553039075009</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>13.20754716981132</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>13.12371838687628</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>12.98860388284643</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>12.95178421334148</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>12.88081580624602</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>12.86503669303267</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>12.77884324215201</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>12.63432381756547</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>12.37183868762816</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>12.37093690248566</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>12.32632249840663</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>12.24115534499885</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>12.19341935412385</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>12.17565611195664</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>12.09842788790157</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>11.71535691748023</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>11.58699808795411</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>11.55344998853824</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>11.40354133412525</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>11.2781954887218</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>11.2019561396806</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>11.05989506867074</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>11.02620921525178</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>10.74997476531745</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>10.52587138191797</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>10.37735849056604</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>10.32504780114723</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>10.2529049897471</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>10.21370121565073</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>10.17855154237351</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>10.15256691042726</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>10.03163452429099</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>9.90566037735849</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>9.780090149379758</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>9.705089838948009</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>9.536359924273359</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>9.407489653780155</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>9.246034604069829</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>9.011130255569283</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>8.964592601621062</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>8.962264150943396</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>8.916507329509242</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>8.803844386773124</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>8.718929254302104</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>8.490566037735849</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>8.471061552407088</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>8.395067860380216</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>8.285385500575375</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>8.196224891490864</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>7.62906309751434</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>7.518796992481203</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>7.482895210658985</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>7.450444292549555</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>7.217119208640355</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>7.055994770054128</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>6.846021307597272</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>6.764026393498025</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>6.594330251394513</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>6.581205208438478</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>6.356801093643199</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>6.132075471698113</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>5.604921394395078</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>5.567903840661592</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>5.564053537284895</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>5.188679245283019</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>5.188679245283019</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>5.188679245283019</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>4.963064701733546</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>4.718562576831857</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>4.663369334813768</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>4.658214644928166</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>4.655482845541579</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>4.430495459808641</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>4.161886551943914</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>4.161795910226649</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>4.101161995898838</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>4.095313547443476</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>3.849437618322878</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>3.774738289906014</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>3.732134652875219</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>3.654402543056884</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>3.570102881456407</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>3.532855556677097</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>3.508052676192112</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>3.451542667826415</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>3.434368519737251</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>3.30188679245283</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>3.28976891838736</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>3.262513503781059</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>3.175086842586385</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>3.075871496924128</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>2.964774203407962</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>2.895430416867738</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>2.830188679245283</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>2.8195919614885</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>2.802460697197539</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>2.759719566602932</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>2.746972594008923</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>2.698689632131853</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>2.597402597402597</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>2.597402597402597</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>2.460697197539303</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>2.449979583503471</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>2.441045251752709</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>2.426831236884259</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>2.418295946237929</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>2.392344497607656</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>2.358490566037736</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>2.357907800043213</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>2.264375069601693</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>2.255639097744361</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>2.219829986265266</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>2.200464318158878</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>2.0930550209231</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>2.001274697259401</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>1.915246067845251</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>1.886792452830189</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>1.886792452830189</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>1.886792452830189</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>1.886792452830189</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>1.886792452830189</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>1.88202977096403</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>1.880178457616316</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>1.856045139017781</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>1.845522898154477</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>1.804075875125283</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>1.786615524376703</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>1.778202676864245</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>1.695770667205007</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>1.695770667205007</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>1.681449758724425</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>1.631612492033142</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>1.564550317957</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>1.435406698564593</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>1.42173057648762</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>1.40597539543058</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>1.372766730594529</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>1.332058636073932</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>1.29201574644191</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>1.268434324138458</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>1.260793153511118</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>1.249203314212874</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>1.238001812921411</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>1.213853520917629</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>1.198215423836839</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>1.059856667003129</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>0.9891995558695872</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>0.9433962264150944</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>0.9433962264150944</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>0.916940475280813</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>0.8940169633987927</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>0.8634522808894323</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>0.8558111102620921</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>0.7772282224689614</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>0.7259112095973103</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>0.696477238316342</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>0.6496157986562233</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>0.62734325698801</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>0.6246016571064372</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>0.5960113089325285</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>0.5955385081255677</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>0.5854446351064904</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>0.5605256319833698</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>0.5195996026591274</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>0.4784688995215311</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>0.4730979846770889</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>0.4716981132075472</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>0.4716981132075472</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>0.4661114082677466</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>0.4270235818992989</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>0.2063116069381829</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>0.2050580997949419</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>0.1451822419194621</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>0.1019757807520714</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>0.08537807639481793</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>0.08075098415261936</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>0.06605987607564601</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>0.06112936501872087</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>0.06009958650491103</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>0.04867569816100232</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>0.03988941766990399</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>0.03820585313670054</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>0.02549394518801784</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>0.02105274821467155</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>0.01856045139017781</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>0.001108039379719555</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
